--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9407.09</v>
+        <v>9308.58</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35851.44</v>
+        <v>35655.1</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>60791.01</v>
+        <v>60713.64</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>28758.98</v>
+        <v>28961.95</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15587.37</v>
+        <v>15389.38</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>42607.59</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>72905.19</v>
+        <v>72747.41</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>109847.59</v>
+        <v>110786.33</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>52168.28</v>
+        <v>52642.79</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>59360.57</v>
+        <v>59900.5</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40651.96</v>
+        <v>40610.03</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>124329.61</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="14">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>155676.55</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="15">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>33990.91</v>
+        <v>34607.19</v>
       </c>
     </row>
     <row r="16">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38513.09</v>
+        <v>38546.27</v>
       </c>
     </row>
     <row r="17">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>75876.05</v>
+        <v>75440.2</v>
       </c>
     </row>
     <row r="18">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13652.08</v>
+        <v>13334.4</v>
       </c>
     </row>
     <row r="19">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>25595.22</v>
+        <v>24779.07</v>
       </c>
     </row>
     <row r="20">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>61900.28</v>
+        <v>60270.24</v>
       </c>
     </row>
     <row r="21">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>26973.2</v>
+        <v>27305.16</v>
       </c>
     </row>
     <row r="22">
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>56220.72</v>
+        <v>56849.47</v>
       </c>
     </row>
     <row r="23">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>47069.77</v>
+        <v>47516.97</v>
       </c>
     </row>
     <row r="24">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14650.23</v>
+        <v>14759.37</v>
       </c>
     </row>
     <row r="25">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>36985.96</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="26">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>38823.26</v>
+        <v>39013.97</v>
       </c>
     </row>
     <row r="27">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13548.53</v>
+        <v>13591.65</v>
       </c>
     </row>
     <row r="28">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>13838.47</v>
+        <v>13882.51</v>
       </c>
     </row>
     <row r="29">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>54587.71</v>
+        <v>54877.98</v>
       </c>
     </row>
     <row r="30">
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>19031.32</v>
+        <v>19209.82</v>
       </c>
     </row>
     <row r="31">
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>14167.34</v>
+        <v>14059.86</v>
       </c>
     </row>
     <row r="32">
@@ -2411,7 +2411,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>61945.41</v>
+        <v>61066.26</v>
       </c>
     </row>
     <row r="33">
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>42741.95</v>
+        <v>43554.54</v>
       </c>
     </row>
     <row r="34">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22297.04</v>
+        <v>22799.9</v>
       </c>
     </row>
     <row r="35">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>31415.2</v>
+        <v>31332.11</v>
       </c>
     </row>
     <row r="36">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>30100.91</v>
+        <v>29511.72</v>
       </c>
     </row>
     <row r="37">
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1249.55</v>
+        <v>1225.1</v>
       </c>
     </row>
     <row r="38">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>33208.46</v>
+        <v>32525.97</v>
       </c>
     </row>
     <row r="39">
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>58737.79</v>
+        <v>59295.73</v>
       </c>
     </row>
     <row r="40">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>17598.1</v>
+        <v>17666.79</v>
       </c>
     </row>
     <row r="41">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30664.9</v>
+        <v>30973.31</v>
       </c>
     </row>
     <row r="42">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41999.21</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="43">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1362.08</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="44">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>32200.06</v>
+        <v>32021.55</v>
       </c>
     </row>
     <row r="45">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>32092.94</v>
+        <v>31935.15</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1133353-33-CM25</t>
+          <t>2827-549-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9308.58</v>
+        <v>20149.31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1133353-35-CM25</t>
+          <t>2292-1116-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35655.1</v>
+        <v>34405.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1209004-234-CM25</t>
+          <t>1133353-33-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>60713.64</v>
+        <v>9308.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>552578-137-CM25</t>
+          <t>1133353-35-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +712,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>28961.95</v>
+        <v>35655.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4314-561-CM25</t>
+          <t>1209004-234-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>15389.38</v>
+        <v>60713.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3311-137-CM25</t>
+          <t>552578-137-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>42066.38</v>
+        <v>28961.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4473-4635-CM25</t>
+          <t>4314-561-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,22 +895,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>72747.41</v>
+        <v>15389.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1596-387-CM25</t>
+          <t>3311-137-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,32 +981,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>110786.33</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3287-67-CM26</t>
+          <t>4473-4635-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>52642.79</v>
+        <v>72747.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3287-68-CM26</t>
+          <t>1596-387-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1077,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,28 +1103,32 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>59900.5</v>
+        <v>110786.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4451-105-CM26</t>
+          <t>3287-68-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40610.03</v>
+        <v>59900.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1596-40-CM26</t>
+          <t>3287-67-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,22 +1204,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,32 +1229,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>123574.14</v>
+        <v>52642.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1596-42-CM26</t>
+          <t>4451-105-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1269,7 +1265,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1279,12 +1275,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1294,32 +1290,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>154730.6</v>
+        <v>40610.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3756-156-CM26</t>
+          <t>1596-40-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1329,12 +1321,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1344,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1359,28 +1351,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>34607.19</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3469-143-CM26</t>
+          <t>1596-42-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1390,12 +1386,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1405,12 +1401,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1420,28 +1416,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>38546.27</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1508755-4-CM26</t>
+          <t>3756-156-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Compras GORE Maule</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>75440.2</v>
+        <v>34607.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1133353-19-CM26</t>
+          <t>3469-143-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1557,28 +1557,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13334.4</v>
+        <v>38546.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4690-89-CM26</t>
+          <t>1508755-4-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>Compras GORE Maule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1618,43 +1618,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>24779.07</v>
+        <v>75440.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4511-39-CM26</t>
+          <t>1133353-19-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1664,12 +1664,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>60270.24</v>
+        <v>13334.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4401-291-CM26</t>
+          <t>4690-89-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27305.16</v>
+        <v>24779.07</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2335-303-CM26</t>
+          <t>4511-39-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>Ilustre Municipalidad de Retiro</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>56849.47</v>
+        <v>60270.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3756-348-CM26</t>
+          <t>4401-291-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>47516.97</v>
+        <v>27305.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1133353-29-CM26</t>
+          <t>2335-303-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1883,22 +1883,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14759.37</v>
+        <v>56849.47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1596-123-CM26</t>
+          <t>3756-348-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1944,22 +1944,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>36894.63</v>
+        <v>47516.97</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3807-213-CM26</t>
+          <t>1133353-29-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>39013.97</v>
+        <v>14759.37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4690-165-CM26</t>
+          <t>1596-123-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,12 +2091,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2106,13 +2106,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13591.65</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2436-600-CM26</t>
+          <t>3807-213-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>13882.51</v>
+        <v>39013.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2337-48-CM26</t>
+          <t>4690-165-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>54877.98</v>
+        <v>13591.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4316-25-CM26</t>
+          <t>2436-600-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2289,13 +2289,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>19209.82</v>
+        <v>13882.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2436-650-CM26</t>
+          <t>2337-48-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>14059.86</v>
+        <v>54877.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>906973-28-CM26</t>
+          <t>4316-25-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2371,22 +2371,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2411,13 +2411,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>61066.26</v>
+        <v>19209.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2436-705-CM26</t>
+          <t>2436-650-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2457,12 +2457,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.068.830-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>43554.54</v>
+        <v>14059.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2337-55-CM26</t>
+          <t>906973-28-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22799.9</v>
+        <v>61066.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2337-57-CM26</t>
+          <t>2436-705-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.068.830-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>31332.11</v>
+        <v>43554.54</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1426095-155-CM26</t>
+          <t>2337-55-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>29511.72</v>
+        <v>22799.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1426095-156-CM26</t>
+          <t>2337-57-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1225.1</v>
+        <v>31332.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4314-256-CM26</t>
+          <t>1426095-155-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2777,13 +2777,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32525.97</v>
+        <v>29511.72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2320-236-CM26</t>
+          <t>1426095-156-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>59295.73</v>
+        <v>1225.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4314-265-CM26</t>
+          <t>4314-256-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2899,13 +2899,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>17666.79</v>
+        <v>32525.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3505-168-CM26</t>
+          <t>2320-236-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.110.800-7</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>30973.31</v>
+        <v>59295.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>4314-265-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>41321.44</v>
+        <v>17666.79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>3505-168-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.800-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE PENCAHUE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1340.1</v>
+        <v>30973.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3880-345-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>32021.55</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2291-1276-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3204,6 +3204,128 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
+        <v>1340.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3880-345-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>32021.55</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2291-1276-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
         <v>31935.15</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2827-549-CM25</t>
+          <t>3880-39-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20149.31</v>
+        <v>28089.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2292-1116-CM25</t>
+          <t>4089-34-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34405.31</v>
+        <v>22263.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1133353-33-CM25</t>
+          <t>4089-35-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9308.58</v>
+        <v>47236.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1133353-35-CM25</t>
+          <t>2318-135-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>35655.1</v>
+        <v>35274.87</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1209004-234-CM25</t>
+          <t>2827-94-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>60713.64</v>
+        <v>30450.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>552578-137-CM25</t>
+          <t>3469-125-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28961.95</v>
+        <v>15171.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4314-561-CM25</t>
+          <t>1719-43-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>15389.38</v>
+        <v>34601.98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3311-137-CM25</t>
+          <t>2292-226-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>42066.38</v>
+        <v>35197.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4473-4635-CM25</t>
+          <t>4089-98-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.130.602-k</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>72747.41</v>
+        <v>11833.84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1596-387-CM25</t>
+          <t>1719-63-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,32 +1103,28 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>110786.33</v>
+        <v>29772.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3287-68-CM26</t>
+          <t>1426095-67-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>59900.5</v>
+        <v>25556.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3287-67-CM26</t>
+          <t>2595-161-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1244,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>52642.79</v>
+        <v>55160.83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4451-105-CM26</t>
+          <t>2311-2777-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>40610.03</v>
+        <v>23109.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1596-40-CM26</t>
+          <t>1422035-4-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>65.034.681-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,32 +1347,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de los Lagos </t>
-        </is>
-      </c>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>123574.14</v>
+        <v>41358.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1596-42-CM26</t>
+          <t>2311-2837-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1401,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,32 +1408,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>154730.6</v>
+        <v>28645.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3756-156-CM26</t>
+          <t>4085-272-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1451,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1466,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1481,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1496,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>34607.19</v>
+        <v>35593.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3469-143-CM26</t>
+          <t>4605-112-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1512,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1527,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>61.819.000-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1542,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1557,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38546.27</v>
+        <v>25474.48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1508755-4-CM26</t>
+          <t>4511-45-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1573,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Compras GORE Maule</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1603,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1618,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>75440.2</v>
+        <v>30428.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1133353-19-CM26</t>
+          <t>3756-320-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1634,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1649,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1664,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1679,43 +1667,43 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13334.4</v>
+        <v>27090.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4690-89-CM26</t>
+          <t>3696-163-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1725,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1740,43 +1728,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>24779.07</v>
+        <v>12793.58</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4511-39-CM26</t>
+          <t>2595-287-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1786,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>60270.24</v>
+        <v>34535.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4401-291-CM26</t>
+          <t>2595-314-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1847,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1862,43 +1850,43 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>27305.16</v>
+        <v>26897.05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2335-303-CM26</t>
+          <t>2132-125-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1908,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1923,28 +1911,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>56849.47</v>
+        <v>29837.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3756-348-CM26</t>
+          <t>1596-160-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1954,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1969,58 +1957,62 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>47516.97</v>
+        <v>213461.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1133353-29-CM26</t>
+          <t>434-379-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.120.400-6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE CAUQUENES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2030,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2045,43 +2037,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14759.37</v>
+        <v>17686.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1596-123-CM26</t>
+          <t>2827-549-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2091,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2106,43 +2098,43 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>36894.63</v>
+        <v>20149.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3807-213-CM26</t>
+          <t>2318-669-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2152,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2167,43 +2159,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>39013.97</v>
+        <v>48246.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4690-165-CM26</t>
+          <t>2595-347-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2213,58 +2205,62 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>13591.65</v>
+        <v>67443.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2436-600-CM26</t>
+          <t>2318-702-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,12 +2270,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2289,28 +2285,28 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>13882.51</v>
+        <v>37282.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2337-48-CM26</t>
+          <t>1208066-266-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2320,12 +2316,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2335,12 +2331,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2350,28 +2346,28 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>54877.98</v>
+        <v>22469.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4316-25-CM26</t>
+          <t>2292-1116-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2381,12 +2377,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2396,12 +2392,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2411,43 +2407,43 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>19209.82</v>
+        <v>34405.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2436-650-CM26</t>
+          <t>1596-208-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2465,35 +2461,39 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14059.86</v>
+        <v>133329.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>906973-28-CM26</t>
+          <t>1596-206-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2518,58 +2518,62 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>61066.26</v>
+        <v>149130.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2436-705-CM26</t>
+          <t>4605-188-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.819.000-5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2579,12 +2583,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.068.830-0</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2594,43 +2598,43 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>43554.54</v>
+        <v>24716.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2337-55-CM26</t>
+          <t>3756-657-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2640,12 +2644,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2655,28 +2659,28 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>22799.9</v>
+        <v>68977.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2337-57-CM26</t>
+          <t>707420-103-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2686,12 +2690,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2701,12 +2705,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2716,43 +2720,43 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>31332.11</v>
+        <v>32369.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1426095-155-CM26</t>
+          <t>2827-804-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2762,12 +2766,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2777,43 +2781,43 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29511.72</v>
+        <v>59738.26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1426095-156-CM26</t>
+          <t>4451-750-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2823,12 +2827,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Cecor S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.010.151-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2838,43 +2842,43 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1225.1</v>
+        <v>43241.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4314-256-CM26</t>
+          <t>1133353-33-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2884,12 +2888,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2899,43 +2903,43 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>32525.97</v>
+        <v>9308.58</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2320-236-CM26</t>
+          <t>1133353-35-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,12 +2949,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2960,43 +2964,43 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>59295.73</v>
+        <v>35655.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4314-265-CM26</t>
+          <t>1209004-234-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,12 +3010,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3021,28 +3025,28 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>17666.79</v>
+        <v>60713.64</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3505-168-CM26</t>
+          <t>552578-137-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3052,12 +3056,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.110.800-7</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,12 +3071,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,43 +3086,43 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>30973.31</v>
+        <v>28961.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>3311-137-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3128,12 +3132,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3143,28 +3147,28 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>41321.44</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>4314-561-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3174,12 +3178,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,12 +3193,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3204,43 +3208,43 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1340.1</v>
+        <v>15389.38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3880-345-CM26</t>
+          <t>4473-4635-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3250,12 +3254,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3265,68 +3269,2402 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>32021.55</v>
+        <v>72747.41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>1596-387-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>110786.33</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3287-67-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.100.500-3</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>52642.79</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3287-68-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.100.500-3</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>59900.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4451-105-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>40610.03</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1596-40-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>123574.14</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1596-42-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>154730.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3756-156-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>34607.19</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3469-143-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.120.300-k</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>38546.27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1508755-4-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.004.051-9</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Compras GORE Maule</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>75440.2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1133353-19-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>13334.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4690-89-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>24779.07</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4511-39-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.130.800-6</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Retiro</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>60270.24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4401-291-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>27305.16</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2335-303-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>69.130.301-2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>56849.47</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3756-348-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.110.600-4</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>47516.97</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1133353-29-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.100.400-7</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>14759.37</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1596-123-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>36894.63</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3807-213-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.120.200-3</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>39013.97</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4690-165-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>13591.65</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2436-600-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>13882.51</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2337-48-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>69.130.300-4</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LINARES</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>54877.98</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4316-25-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.110.300-5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>19209.82</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2436-650-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>14059.86</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>906973-28-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.100.700-6</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>61066.26</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2436-705-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>78.068.830-0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>43554.54</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2337-55-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.130.300-4</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LINARES</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>22799.9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2337-57-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.130.300-4</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LINARES</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>31332.11</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1426095-155-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>29511.72</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1426095-156-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>1225.1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4314-256-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.110.300-5</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>32525.97</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2320-236-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>59295.73</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4314-265-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.110.300-5</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>17666.79</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3505-168-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.110.800-7</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>30973.31</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1596-185-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>41321.44</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1596-186-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>1340.1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3880-345-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>32021.55</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>2291-1276-CM26</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>69.110.400-1</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
         <is>
           <t>SUMMIT STORE SPA</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="n">
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
         <v>31935.15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3880-394-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>56890.75</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1596-199-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>113982.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2909,7 +2909,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1133353-35-CM25</t>
+          <t>1389488-69-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.981.320-0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE LOS ÁLAMOS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2964,13 +2964,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>35655.1</v>
+        <v>23648.08</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1209004-234-CM25</t>
+          <t>1133353-35-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>60713.64</v>
+        <v>35655.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>552578-137-CM25</t>
+          <t>1209004-234-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>28961.95</v>
+        <v>60713.64</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3311-137-CM25</t>
+          <t>552578-137-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3102,27 +3102,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3147,13 +3147,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>42066.38</v>
+        <v>28961.95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4314-561-CM25</t>
+          <t>3311-137-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3208,13 +3208,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>15389.38</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4473-4635-CM25</t>
+          <t>4314-561-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3229,22 +3229,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.100.200-4</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>72747.41</v>
+        <v>15389.38</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1596-387-CM25</t>
+          <t>4473-4635-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.100.200-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3315,32 +3315,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>110786.33</v>
+        <v>72747.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3287-67-CM26</t>
+          <t>1596-387-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3350,27 +3346,27 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3388,20 +3384,24 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>52642.79</v>
+        <v>110786.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3287-68-CM26</t>
+          <t>3287-67-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3456,13 +3456,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>59900.5</v>
+        <v>52642.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4451-105-CM26</t>
+          <t>3287-68-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3477,22 +3477,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.349.970-7</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3517,13 +3517,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>40610.03</v>
+        <v>59900.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1596-40-CM26</t>
+          <t>4451-105-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3563,32 +3563,28 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>123574.14</v>
+        <v>40610.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1596-42-CM26</t>
+          <t>1596-40-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3628,17 +3624,17 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3647,13 +3643,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>154730.6</v>
+        <v>123574.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3756-156-CM26</t>
+          <t>1596-42-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3663,12 +3659,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3678,12 +3674,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3693,28 +3689,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>34607.19</v>
+        <v>154730.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3469-143-CM26</t>
+          <t>3756-156-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.120.300-k</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANCO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>38546.27</v>
+        <v>34607.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1508755-4-CM26</t>
+          <t>3469-143-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.120.300-k</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Compras GORE Maule</t>
+          <t>I MUNICIPALIDAD DE CHANCO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3830,13 +3830,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>75440.2</v>
+        <v>38546.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1133353-19-CM26</t>
+          <t>1508755-4-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3851,22 +3851,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3876,12 +3876,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3891,43 +3891,43 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>13334.4</v>
+        <v>75440.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4690-89-CM26</t>
+          <t>1133353-19-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3952,18 +3952,18 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>24779.07</v>
+        <v>13334.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4511-39-CM26</t>
+          <t>4690-89-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.130.800-6</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4013,18 +4013,18 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>60270.24</v>
+        <v>24779.07</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4401-291-CM26</t>
+          <t>4511-39-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4034,22 +4034,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.130.800-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4074,13 +4074,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>27305.16</v>
+        <v>60270.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2335-303-CM26</t>
+          <t>4401-291-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4090,27 +4090,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>56849.47</v>
+        <v>27305.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3756-348-CM26</t>
+          <t>2335-303-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4156,22 +4156,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>47516.97</v>
+        <v>56849.47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1133353-29-CM26</t>
+          <t>3756-348-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>14759.37</v>
+        <v>47516.97</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1596-123-CM26</t>
+          <t>1133353-29-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>36894.63</v>
+        <v>14759.37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3807-213-CM26</t>
+          <t>1596-123-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4379,13 +4379,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>39013.97</v>
+        <v>36894.63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4690-165-CM26</t>
+          <t>3807-213-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>13591.65</v>
+        <v>39013.97</v>
       </c>
     </row>
     <row r="66">
@@ -4507,7 +4507,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2337-48-CM26</t>
+          <t>4690-165-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4562,13 +4562,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>54877.98</v>
+        <v>13591.65</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4316-25-CM26</t>
+          <t>2337-48-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>19209.82</v>
+        <v>54877.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2436-650-CM26</t>
+          <t>4316-25-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4684,13 +4684,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>14059.86</v>
+        <v>19209.82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>906973-28-CM26</t>
+          <t>2436-650-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4705,22 +4705,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.100.700-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>61066.26</v>
+        <v>14059.86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2436-705-CM26</t>
+          <t>906973-28-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4766,22 +4766,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.100.700-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE VICHUQUEN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>78.068.830-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4806,13 +4806,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>43554.54</v>
+        <v>61066.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2337-55-CM26</t>
+          <t>2436-705-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL AUTOMOTRIZ COADIG LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.068.830-0</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>22799.9</v>
+        <v>43554.54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2337-57-CM26</t>
+          <t>2337-55-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>31332.11</v>
+        <v>22799.9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1426095-155-CM26</t>
+          <t>2337-57-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4989,13 +4989,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>29511.72</v>
+        <v>31332.11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1426095-156-CM26</t>
+          <t>1426095-155-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1225.1</v>
+        <v>29511.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4314-256-CM26</t>
+          <t>1426095-156-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>32525.97</v>
+        <v>1225.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2320-236-CM26</t>
+          <t>4314-256-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5172,13 +5172,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>59295.73</v>
+        <v>32525.97</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4314-265-CM26</t>
+          <t>2320-236-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>17666.79</v>
+        <v>59295.73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3505-168-CM26</t>
+          <t>4314-265-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.110.800-7</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCAHUE</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>30973.31</v>
+        <v>17666.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>3505-168-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.110.800-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE PENCAHUE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>41321.44</v>
+        <v>30973.31</v>
       </c>
     </row>
     <row r="81">
@@ -5422,7 +5422,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3880-345-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5477,13 +5477,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>32021.55</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2291-1276-CM26</t>
+          <t>1422035-16-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>65.034.681-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>31935.15</v>
+        <v>31707.78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3880-394-CM26</t>
+          <t>3880-345-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5599,72 +5599,686 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>56890.75</v>
+        <v>32021.55</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>2291-1276-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>31935.15</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>3880-394-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>56890.75</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>1596-199-CM26</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>ago-2026</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>72.227.000-2</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
         <is>
           <t>KOVACS SPA</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="n">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
         <v>113982.42</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4168-1233-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>53039.13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4168-1234-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1924.22</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2318-781-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>69.130.100-1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>35376.64</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4085-625-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.130.600-3</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>60576.41</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4085-626-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.130.600-3</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>1213.17</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1738-372-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.130.200-8</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>25888.05</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>3880-478-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>35817.03</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1596-228-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>79.853.470-K</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>122392.49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -562,7 +562,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1923,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1988,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2118,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2183,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2248,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2278,7 +2378,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2339,7 +2443,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2400,7 +2508,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2591,7 +2703,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2652,7 +2768,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2713,7 +2833,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2774,7 +2898,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2957,7 +3085,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3018,7 +3150,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3079,7 +3215,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3140,7 +3280,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3201,7 +3345,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3323,7 +3471,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3449,7 +3601,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3571,7 +3727,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3762,7 +3922,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3823,7 +3987,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3884,7 +4052,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4006,7 +4178,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4067,7 +4243,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4128,7 +4308,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4189,7 +4373,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4250,7 +4438,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4311,7 +4503,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4372,7 +4568,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4433,7 +4633,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4555,7 +4759,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4616,7 +4824,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4677,7 +4889,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4738,7 +4954,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4799,7 +5019,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4921,7 +5145,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4982,7 +5210,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5043,7 +5275,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5104,7 +5340,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5165,7 +5405,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5226,7 +5470,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5348,7 +5596,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5409,7 +5661,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5470,7 +5726,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5531,7 +5791,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5592,7 +5856,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5653,7 +5921,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5840,7 +6112,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5901,7 +6177,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5962,7 +6242,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6145,7 +6429,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6206,7 +6494,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -5986,7 +5986,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M95"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4650,7 +4650,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2436-600-CM26</t>
+          <t>4690-165-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4690,28 +4690,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>13882.51</v>
+        <v>13591.65</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4690-165-CM26</t>
+          <t>2436-600-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4736,12 +4740,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4751,26 +4755,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13591.65</v>
+        <v>13882.51</v>
       </c>
     </row>
     <row r="68">
@@ -5613,7 +5613,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5672,13 +5672,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1340.1</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>41321.44</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="83">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6198,7 +6198,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2318-781-CM26</t>
+          <t>4085-626-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6238,26 +6238,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>35376.64</v>
+        <v>1213.17</v>
       </c>
     </row>
     <row r="91">
@@ -6324,7 +6320,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4085-626-CM26</t>
+          <t>2318-781-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6349,12 +6345,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6364,22 +6360,26 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>1213.17</v>
+        <v>35376.64</v>
       </c>
     </row>
     <row r="93">
@@ -6575,6 +6575,266 @@
       </c>
       <c r="M95" s="2" t="n">
         <v>122392.49</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>3880-485-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MAULE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>62251.02</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2292-7295-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>25794.34</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1596-280-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>68043.28999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1596-281-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>72.227.000-2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL VII REGION</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>882.47</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -4540,7 +4540,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M99"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4650,7 +4650,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4690-165-CM26</t>
+          <t>2436-600-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4690,32 +4690,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>91.139.000-0</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>13591.65</v>
+        <v>13882.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2436-600-CM26</t>
+          <t>4690-165-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4740,12 +4736,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4755,22 +4751,26 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>13882.51</v>
+        <v>13591.65</v>
       </c>
     </row>
     <row r="68">
@@ -5613,7 +5613,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5672,13 +5672,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>41321.44</v>
+        <v>1340.1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>1340.1</v>
+        <v>41321.44</v>
       </c>
     </row>
     <row r="83">
@@ -6259,7 +6259,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4085-625-CM26</t>
+          <t>2318-781-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.130.100-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6299,28 +6299,32 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>60576.41</v>
+        <v>35376.64</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2318-781-CM26</t>
+          <t>4085-625-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6345,12 +6349,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.130.100-1</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6360,26 +6364,22 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>35376.64</v>
+        <v>60576.41</v>
       </c>
     </row>
     <row r="93">
@@ -6710,7 +6710,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1596-280-CM26</t>
+          <t>1596-281-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>68043.28999999999</v>
+        <v>882.47</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1596-281-CM26</t>
+          <t>1596-280-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6834,7 +6834,68 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>882.47</v>
+        <v>68043.28999999999</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4473-384-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.100.200-4</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>I.MUNICIPALIDAD DE ROMERAL</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ BALMACEDA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>86.341.100-9</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>24374.9</v>
       </c>
     </row>
   </sheetData>
